--- a/docs/oc-mensuales/administracion-y-entrega-de-beneficios/may-2026.xlsx
+++ b/docs/oc-mensuales/administracion-y-entrega-de-beneficios/may-2026.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>16710.57</v>
+        <v>16610.42</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>1637.24</v>
+        <v>1627.43</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>9702.799999999999</v>
+        <v>9644.65</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>9402.76</v>
+        <v>9346.41</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>13411.3</v>
+        <v>13330.93</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>947.52</v>
+        <v>941.85</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>719.67</v>
+        <v>715.35</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>32303.47</v>
+        <v>32109.87</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>11855.45</v>
+        <v>11784.4</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>3676.32</v>
+        <v>3654.28</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>846.67</v>
+        <v>841.59</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>10509.25</v>
+        <v>10446.26</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>11998.96</v>
+        <v>11835.83</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>8035.92</v>
+        <v>7926.67</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>24341.66</v>
+        <v>24010.72</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>1639.74</v>
+        <v>1617.44</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>325.97</v>
+        <v>321.54</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>6274.29</v>
+        <v>6188.99</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>5117.06</v>
+        <v>5047.49</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>69611.34</v>
+        <v>68664.92999999999</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>57151.98</v>
+        <v>56374.97</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>140680.11</v>
+        <v>138767.48</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>22201.71</v>
+        <v>21899.87</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>4702.34</v>
+        <v>4638.41</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>22617.7</v>
+        <v>22310.19</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>892.39</v>
+        <v>880.25</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>5037.67</v>
+        <v>4969.18</v>
       </c>
     </row>
     <row r="29">
@@ -2220,7 +2220,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>118891.71</v>
+        <v>117275.31</v>
       </c>
     </row>
     <row r="30">
@@ -2281,7 +2281,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>1659.47</v>
+        <v>1636.91</v>
       </c>
     </row>
     <row r="31">
@@ -2342,7 +2342,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>16719.12</v>
+        <v>16576.52</v>
       </c>
     </row>
     <row r="32">
@@ -2403,7 +2403,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>927.1</v>
+        <v>919.1900000000001</v>
       </c>
     </row>
     <row r="33">
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>662.84</v>
+        <v>657.1900000000001</v>
       </c>
     </row>
     <row r="34">
@@ -2525,7 +2525,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>13853.58</v>
+        <v>13735.42</v>
       </c>
     </row>
     <row r="35">
@@ -2586,7 +2586,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>3920.07</v>
+        <v>3886.63</v>
       </c>
     </row>
     <row r="36">
@@ -2647,7 +2647,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>2229.17</v>
+        <v>2210.15</v>
       </c>
     </row>
     <row r="37">
@@ -2708,7 +2708,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>15367</v>
+        <v>15235.93</v>
       </c>
     </row>
     <row r="38">
@@ -2769,7 +2769,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>6426.2</v>
+        <v>6371.39</v>
       </c>
     </row>
     <row r="39">
@@ -2830,7 +2830,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>19606.64</v>
+        <v>19439.41</v>
       </c>
     </row>
     <row r="40">
@@ -2891,7 +2891,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>1243.54</v>
+        <v>1232.94</v>
       </c>
     </row>
     <row r="41">
@@ -2952,7 +2952,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>390.52</v>
+        <v>387.19</v>
       </c>
     </row>
     <row r="42">
@@ -3013,7 +3013,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>1807.63</v>
+        <v>1792.22</v>
       </c>
     </row>
     <row r="43">
@@ -3074,7 +3074,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>650.87</v>
+        <v>645.3200000000001</v>
       </c>
     </row>
     <row r="44">
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>49029.09</v>
+        <v>48610.9</v>
       </c>
     </row>
     <row r="45">
@@ -3196,7 +3196,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>2453.34</v>
+        <v>2432.42</v>
       </c>
     </row>
     <row r="46">
@@ -3257,7 +3257,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>600.08</v>
+        <v>594.96</v>
       </c>
     </row>
     <row r="47">
@@ -3318,7 +3318,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>4026.35</v>
+        <v>3992.01</v>
       </c>
     </row>
     <row r="48">
@@ -3379,7 +3379,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>1588.17</v>
+        <v>1574.62</v>
       </c>
     </row>
     <row r="49">
@@ -3440,7 +3440,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>1455.82</v>
+        <v>1443.4</v>
       </c>
     </row>
     <row r="50">
@@ -3501,7 +3501,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>14482.46</v>
+        <v>14358.93</v>
       </c>
     </row>
     <row r="51">
@@ -3562,7 +3562,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>16710.53</v>
+        <v>16568</v>
       </c>
     </row>
     <row r="52">
@@ -3623,7 +3623,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>23812.5</v>
+        <v>23940.73</v>
       </c>
     </row>
     <row r="53">
@@ -3684,7 +3684,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>1873.78</v>
+        <v>1883.87</v>
       </c>
     </row>
     <row r="54">
@@ -3745,7 +3745,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>25188.86</v>
+        <v>25324.5</v>
       </c>
     </row>
     <row r="55">
@@ -3806,7 +3806,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>77759.64</v>
+        <v>78178.38</v>
       </c>
     </row>
     <row r="56">
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>29856.3</v>
+        <v>30017.08</v>
       </c>
     </row>
     <row r="57">
@@ -3928,7 +3928,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>426.45</v>
+        <v>428.75</v>
       </c>
     </row>
     <row r="58">
@@ -3989,7 +3989,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>21246.04</v>
+        <v>21360.45</v>
       </c>
     </row>
     <row r="59">
@@ -4050,7 +4050,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>2209.8</v>
+        <v>2221.7</v>
       </c>
     </row>
     <row r="60">
@@ -4111,7 +4111,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>15663.87</v>
+        <v>15748.22</v>
       </c>
     </row>
     <row r="61">
@@ -4172,7 +4172,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>33454.47</v>
+        <v>33634.62</v>
       </c>
     </row>
     <row r="62">
@@ -4233,7 +4233,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>4785.78</v>
+        <v>4811.55</v>
       </c>
     </row>
     <row r="63">
@@ -4294,7 +4294,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>27833.11</v>
+        <v>27982.99</v>
       </c>
     </row>
     <row r="64">
@@ -4355,7 +4355,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>1671.05</v>
+        <v>1680.05</v>
       </c>
     </row>
     <row r="65">
@@ -4416,7 +4416,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>16510</v>
+        <v>16598.9</v>
       </c>
     </row>
     <row r="66">
@@ -4477,7 +4477,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>32743.38</v>
+        <v>33109.57</v>
       </c>
     </row>
     <row r="67">
@@ -4538,7 +4538,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>13375</v>
+        <v>13524.59</v>
       </c>
     </row>
     <row r="68">
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>2857.5</v>
+        <v>2889.46</v>
       </c>
     </row>
     <row r="69">
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>10438.34</v>
+        <v>10555.08</v>
       </c>
     </row>
     <row r="70">
@@ -4721,7 +4721,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>907.89</v>
+        <v>918.05</v>
       </c>
     </row>
     <row r="71">
@@ -4782,7 +4782,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>9357.889999999999</v>
+        <v>9428.77</v>
       </c>
     </row>
     <row r="72">
@@ -4843,7 +4843,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>9656.09</v>
+        <v>9729.23</v>
       </c>
     </row>
     <row r="73">
@@ -4904,7 +4904,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>3894.21</v>
+        <v>3923.71</v>
       </c>
     </row>
     <row r="74">
@@ -4965,7 +4965,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>5372.45</v>
+        <v>5413.14</v>
       </c>
     </row>
     <row r="75">
@@ -5026,7 +5026,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>17932.4</v>
+        <v>18068.22</v>
       </c>
     </row>
     <row r="76">
@@ -5087,7 +5087,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>14712.74</v>
+        <v>14824.18</v>
       </c>
     </row>
     <row r="77">
@@ -5148,7 +5148,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>35356.58</v>
+        <v>35624.39</v>
       </c>
     </row>
     <row r="78">
@@ -5209,7 +5209,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>3390.9</v>
+        <v>3416.58</v>
       </c>
     </row>
     <row r="79">
@@ -5270,7 +5270,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>28997.06</v>
+        <v>29216.69</v>
       </c>
     </row>
     <row r="80">
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>1335.16</v>
+        <v>1345.27</v>
       </c>
     </row>
     <row r="81">
@@ -5392,7 +5392,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>22225</v>
+        <v>22393.34</v>
       </c>
     </row>
     <row r="82">
@@ -5453,7 +5453,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>1580.97</v>
+        <v>1592.94</v>
       </c>
     </row>
     <row r="83">
@@ -5514,7 +5514,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>2228.07</v>
+        <v>2244.95</v>
       </c>
     </row>
     <row r="84">
@@ -5575,7 +5575,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>14033.5</v>
+        <v>14139.79</v>
       </c>
     </row>
     <row r="85">
@@ -5636,7 +5636,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>11468.1</v>
+        <v>11511.55</v>
       </c>
     </row>
     <row r="86">
@@ -5697,7 +5697,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>26898.92</v>
+        <v>27000.82</v>
       </c>
     </row>
     <row r="87">
@@ -5758,7 +5758,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>9863.67</v>
+        <v>9901.030000000001</v>
       </c>
     </row>
     <row r="88">
@@ -5819,7 +5819,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>1139.82</v>
+        <v>1144.14</v>
       </c>
     </row>
     <row r="89">
@@ -5880,7 +5880,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>5896.95</v>
+        <v>5919.29</v>
       </c>
     </row>
     <row r="90">
@@ -5941,7 +5941,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>2350.56</v>
+        <v>2359.46</v>
       </c>
     </row>
     <row r="91">
@@ -6002,7 +6002,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>46787.32</v>
+        <v>46964.58</v>
       </c>
     </row>
     <row r="92">
@@ -6063,7 +6063,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>8280.4</v>
+        <v>8311.77</v>
       </c>
     </row>
     <row r="93">
@@ -6124,7 +6124,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>11348.84</v>
+        <v>11391.83</v>
       </c>
     </row>
     <row r="94">
@@ -6185,7 +6185,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>334.21</v>
+        <v>335.48</v>
       </c>
     </row>
     <row r="95">
@@ -6246,7 +6246,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>23973.36</v>
+        <v>24064.19</v>
       </c>
     </row>
     <row r="96">
@@ -6307,7 +6307,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>12594.17</v>
+        <v>12641.88</v>
       </c>
     </row>
     <row r="97">
@@ -6368,7 +6368,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>3899.12</v>
+        <v>3913.89</v>
       </c>
     </row>
     <row r="98">
@@ -6429,7 +6429,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>2676.22</v>
+        <v>2686.36</v>
       </c>
     </row>
     <row r="99">
@@ -6490,7 +6490,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>2133.6</v>
+        <v>2128.21</v>
       </c>
     </row>
     <row r="100">
@@ -6551,7 +6551,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>708.6799999999999</v>
+        <v>706.89</v>
       </c>
     </row>
     <row r="101">
@@ -6612,7 +6612,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>2619.57</v>
+        <v>2612.96</v>
       </c>
     </row>
     <row r="102">
@@ -6673,7 +6673,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>9949.389999999999</v>
+        <v>9924.27</v>
       </c>
     </row>
     <row r="103">
@@ -6734,7 +6734,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>38823.95</v>
+        <v>38725.92</v>
       </c>
     </row>
     <row r="104">
@@ -6795,7 +6795,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>1113.94</v>
+        <v>1111.13</v>
       </c>
     </row>
     <row r="105">
@@ -6856,7 +6856,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>20496.95</v>
+        <v>20445.2</v>
       </c>
     </row>
     <row r="106">
@@ -6917,7 +6917,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>3810</v>
+        <v>3800.38</v>
       </c>
     </row>
     <row r="107">
@@ -6978,7 +6978,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>23888.7</v>
+        <v>23828.38</v>
       </c>
     </row>
     <row r="108">
@@ -7039,7 +7039,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>44067.94</v>
+        <v>43956.67</v>
       </c>
     </row>
     <row r="109">
@@ -7100,7 +7100,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>209.55</v>
+        <v>209.02</v>
       </c>
     </row>
     <row r="110">
@@ -7161,7 +7161,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>51361.14</v>
+        <v>51231.46</v>
       </c>
     </row>
     <row r="111">
@@ -7222,7 +7222,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>1114.03</v>
+        <v>1111.22</v>
       </c>
     </row>
     <row r="112">
@@ -7283,7 +7283,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>6301.85</v>
+        <v>6285.93</v>
       </c>
     </row>
     <row r="113">
@@ -7344,7 +7344,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>18897.6</v>
+        <v>18849.88</v>
       </c>
     </row>
     <row r="114">
@@ -7405,7 +7405,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>15139.31</v>
+        <v>15283.14</v>
       </c>
     </row>
     <row r="115">
@@ -7466,7 +7466,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>15220.95</v>
+        <v>15365.56</v>
       </c>
     </row>
     <row r="116">
@@ -7527,7 +7527,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>601.58</v>
+        <v>607.29</v>
       </c>
     </row>
     <row r="117">
@@ -7588,7 +7588,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>9723.969999999999</v>
+        <v>9816.35</v>
       </c>
     </row>
     <row r="118">
@@ -7649,7 +7649,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>39983.3</v>
+        <v>40363.17</v>
       </c>
     </row>
     <row r="119">
@@ -7710,7 +7710,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>4456.14</v>
+        <v>4498.47</v>
       </c>
     </row>
     <row r="120">
@@ -7771,7 +7771,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>444.5</v>
+        <v>448.72</v>
       </c>
     </row>
     <row r="121">
@@ -7832,7 +7832,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>1117.6</v>
+        <v>1128.22</v>
       </c>
     </row>
     <row r="122">
@@ -7893,7 +7893,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>9588.5</v>
+        <v>9679.6</v>
       </c>
     </row>
     <row r="123">
@@ -7954,7 +7954,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>334.21</v>
+        <v>337.39</v>
       </c>
     </row>
     <row r="124">
@@ -8015,7 +8015,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>10924.11</v>
+        <v>11027.9</v>
       </c>
     </row>
     <row r="125">
@@ -8076,7 +8076,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>2542.12</v>
+        <v>2561.06</v>
       </c>
     </row>
     <row r="126">
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>18938.59</v>
+        <v>19079.69</v>
       </c>
     </row>
     <row r="127">
@@ -8198,7 +8198,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>7556.5</v>
+        <v>7612.79</v>
       </c>
     </row>
     <row r="128">
@@ -8259,7 +8259,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>64592.86</v>
+        <v>65074.07</v>
       </c>
     </row>
     <row r="129">
@@ -8320,7 +8320,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>1007.53</v>
+        <v>1015.04</v>
       </c>
     </row>
     <row r="130">
@@ -8381,7 +8381,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>5664.2</v>
+        <v>5706.4</v>
       </c>
     </row>
     <row r="131">
@@ -8442,7 +8442,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>10026.31</v>
+        <v>10101.01</v>
       </c>
     </row>
     <row r="132">
@@ -8503,7 +8503,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>43544.06</v>
+        <v>43868.46</v>
       </c>
     </row>
     <row r="133">
@@ -8564,7 +8564,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>12540.46</v>
+        <v>12633.88</v>
       </c>
     </row>
     <row r="134">
@@ -8625,7 +8625,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>3038.47</v>
+        <v>3061.11</v>
       </c>
     </row>
     <row r="135">
@@ -8686,7 +8686,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>1671.05</v>
+        <v>1683.5</v>
       </c>
     </row>
     <row r="136">
@@ -8747,7 +8747,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>13417.02</v>
+        <v>13516.97</v>
       </c>
     </row>
     <row r="137">
@@ -8808,7 +8808,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>987.38</v>
+        <v>994.73</v>
       </c>
     </row>
     <row r="138">
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>8820.15</v>
+        <v>8885.860000000001</v>
       </c>
     </row>
     <row r="139">
@@ -8930,7 +8930,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>1559.65</v>
+        <v>1571.27</v>
       </c>
     </row>
     <row r="140">
@@ -8991,7 +8991,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>13271.5</v>
+        <v>13370.37</v>
       </c>
     </row>
     <row r="141">
@@ -9052,7 +9052,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>31788.1</v>
+        <v>32024.92</v>
       </c>
     </row>
     <row r="142">
@@ -9113,7 +9113,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>45745.39</v>
+        <v>46086.2</v>
       </c>
     </row>
     <row r="143">
@@ -9174,7 +9174,7 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>122.54</v>
+        <v>123.46</v>
       </c>
     </row>
     <row r="144">
@@ -9235,7 +9235,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>69070.17</v>
+        <v>69584.73</v>
       </c>
     </row>
     <row r="145">
@@ -9296,7 +9296,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>157.41</v>
+        <v>158.59</v>
       </c>
     </row>
     <row r="146">
@@ -9357,7 +9357,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>2616.9</v>
+        <v>2636.39</v>
       </c>
     </row>
     <row r="147">
@@ -9418,7 +9418,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>1795.61</v>
+        <v>1808.99</v>
       </c>
     </row>
     <row r="148">
@@ -9479,7 +9479,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>18454.16</v>
+        <v>18270.12</v>
       </c>
     </row>
     <row r="149">
@@ -9540,7 +9540,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>5340.63</v>
+        <v>5287.37</v>
       </c>
     </row>
     <row r="150">
@@ -9601,7 +9601,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>12496.8</v>
+        <v>12372.17</v>
       </c>
     </row>
     <row r="151">
@@ -9662,7 +9662,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>14157.32</v>
+        <v>14016.14</v>
       </c>
     </row>
     <row r="152">
@@ -9723,7 +9723,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>11747.5</v>
+        <v>11630.34</v>
       </c>
     </row>
     <row r="153">
@@ -9784,7 +9784,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>59097.33</v>
+        <v>58507.96</v>
       </c>
     </row>
     <row r="154">
@@ -9845,7 +9845,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>1073.48</v>
+        <v>1062.78</v>
       </c>
     </row>
     <row r="155">
@@ -9906,7 +9906,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>15596.66</v>
+        <v>15441.12</v>
       </c>
     </row>
     <row r="156">
@@ -9967,7 +9967,7 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>3350.05</v>
+        <v>3316.64</v>
       </c>
     </row>
     <row r="157">
@@ -10028,7 +10028,7 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>5254.9</v>
+        <v>5202.5</v>
       </c>
     </row>
     <row r="158">
@@ -10089,7 +10089,7 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>50663.97</v>
+        <v>50158.71</v>
       </c>
     </row>
     <row r="159">
@@ -10150,7 +10150,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>1375.83</v>
+        <v>1362.11</v>
       </c>
     </row>
     <row r="160">
@@ -10211,7 +10211,7 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>27478.56</v>
+        <v>27204.53</v>
       </c>
     </row>
     <row r="161">
@@ -10272,7 +10272,7 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>60114.44</v>
+        <v>59514.93</v>
       </c>
     </row>
     <row r="162">
@@ -10333,7 +10333,7 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>245.09</v>
+        <v>244.01</v>
       </c>
     </row>
     <row r="163">
@@ -10394,7 +10394,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>17079.59</v>
+        <v>17004.73</v>
       </c>
     </row>
     <row r="164">
@@ -10455,7 +10455,7 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>12773.97</v>
+        <v>12717.98</v>
       </c>
     </row>
     <row r="165">
@@ -10516,7 +10516,7 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>1671.05</v>
+        <v>1663.73</v>
       </c>
     </row>
     <row r="166">
@@ -10577,7 +10577,7 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>891.23</v>
+        <v>887.3200000000001</v>
       </c>
     </row>
     <row r="167">
@@ -10638,7 +10638,7 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>11657.16</v>
+        <v>11606.06</v>
       </c>
     </row>
     <row r="168">
@@ -10699,7 +10699,7 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>392.14</v>
+        <v>390.42</v>
       </c>
     </row>
     <row r="169">
@@ -10760,7 +10760,7 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>6548.97</v>
+        <v>6520.26</v>
       </c>
     </row>
     <row r="170">
@@ -10821,7 +10821,7 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>55.7</v>
+        <v>55.1</v>
       </c>
     </row>
     <row r="171">
@@ -10882,7 +10882,7 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>44634.14</v>
+        <v>44148.6</v>
       </c>
     </row>
     <row r="172">
@@ -10943,7 +10943,7 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>111.4</v>
+        <v>110.19</v>
       </c>
     </row>
     <row r="173">
@@ -11004,7 +11004,7 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>1093.47</v>
+        <v>1081.57</v>
       </c>
     </row>
     <row r="174">
@@ -11065,7 +11065,7 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>73527.17</v>
+        <v>72727.33</v>
       </c>
     </row>
     <row r="175">
@@ -11126,7 +11126,7 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>464.5</v>
+        <v>459.45</v>
       </c>
     </row>
     <row r="176">
@@ -11187,7 +11187,7 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>557.02</v>
+        <v>550.96</v>
       </c>
     </row>
     <row r="177">
@@ -11248,7 +11248,7 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>1002.63</v>
+        <v>991.72</v>
       </c>
     </row>
     <row r="178">
@@ -11309,7 +11309,7 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>2785.09</v>
+        <v>2754.79</v>
       </c>
     </row>
     <row r="179">
@@ -11370,7 +11370,7 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>3200.18</v>
+        <v>3165.37</v>
       </c>
     </row>
     <row r="180">
@@ -11431,7 +11431,7 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>4026.35</v>
+        <v>3982.56</v>
       </c>
     </row>
     <row r="181">
@@ -11492,7 +11492,7 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>13591.62</v>
+        <v>13443.77</v>
       </c>
     </row>
     <row r="182">
@@ -11553,7 +11553,7 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>12538.07</v>
+        <v>12509.62</v>
       </c>
     </row>
     <row r="183">
@@ -11614,7 +11614,7 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>33421.05</v>
+        <v>33345.19</v>
       </c>
     </row>
     <row r="184">
@@ -11675,7 +11675,7 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>38991.22</v>
+        <v>38902.72</v>
       </c>
     </row>
     <row r="185">
@@ -11736,7 +11736,7 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>620.6900000000001</v>
+        <v>619.29</v>
       </c>
     </row>
     <row r="186">
@@ -11801,7 +11801,7 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>247715.57</v>
+        <v>247153.3</v>
       </c>
     </row>
     <row r="187">
@@ -11866,7 +11866,7 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>1146290.69</v>
+        <v>1143688.83</v>
       </c>
     </row>
     <row r="188">
@@ -11927,7 +11927,7 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>19052.91</v>
+        <v>19005.86</v>
       </c>
     </row>
     <row r="189">
@@ -11988,7 +11988,7 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>869.42</v>
+        <v>867.27</v>
       </c>
     </row>
     <row r="190">
@@ -12049,7 +12049,7 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>19658.82</v>
+        <v>19610.27</v>
       </c>
     </row>
     <row r="191">
@@ -12110,7 +12110,7 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>5558.32</v>
+        <v>5544.6</v>
       </c>
     </row>
     <row r="192">
@@ -12171,7 +12171,7 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>56234.53</v>
+        <v>56095.67</v>
       </c>
     </row>
     <row r="193">
@@ -12232,7 +12232,7 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>20052.63</v>
+        <v>20003.11</v>
       </c>
     </row>
     <row r="194">
@@ -12293,7 +12293,7 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>5163.15</v>
+        <v>5150.4</v>
       </c>
     </row>
     <row r="195">
@@ -12354,7 +12354,7 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>623.41</v>
+        <v>621.87</v>
       </c>
     </row>
     <row r="196">
@@ -12415,7 +12415,7 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>6099.76</v>
+        <v>6084.7</v>
       </c>
     </row>
     <row r="197">
@@ -12476,7 +12476,7 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>19524.58</v>
+        <v>19476.37</v>
       </c>
     </row>
     <row r="198">
@@ -12537,7 +12537,7 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>2744.98</v>
+        <v>2738.2</v>
       </c>
     </row>
     <row r="199">
@@ -12598,7 +12598,7 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>1470.53</v>
+        <v>1466.89</v>
       </c>
     </row>
     <row r="200">
@@ -12659,7 +12659,7 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>222.81</v>
+        <v>222.26</v>
       </c>
     </row>
     <row r="201">
@@ -12720,7 +12720,7 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>38910.68</v>
+        <v>39101.82</v>
       </c>
     </row>
     <row r="202">
@@ -12781,7 +12781,7 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>50864.55</v>
+        <v>51114.41</v>
       </c>
     </row>
     <row r="203">
@@ -12842,7 +12842,7 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>508</v>
+        <v>510.49</v>
       </c>
     </row>
     <row r="204">
@@ -12903,7 +12903,7 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>11693.52</v>
+        <v>11750.97</v>
       </c>
     </row>
     <row r="205">
@@ -12964,7 +12964,7 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>58208.33</v>
+        <v>58494.26</v>
       </c>
     </row>
     <row r="206">
@@ -13025,7 +13025,7 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>334.21</v>
+        <v>335.85</v>
       </c>
     </row>
     <row r="207">
@@ -13086,7 +13086,7 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>2005.26</v>
+        <v>2015.11</v>
       </c>
     </row>
     <row r="208">
@@ -13147,7 +13147,7 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>16750.24</v>
+        <v>16832.52</v>
       </c>
     </row>
     <row r="209">
@@ -13208,7 +13208,7 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>294.11</v>
+        <v>295.55</v>
       </c>
     </row>
     <row r="210">
@@ -13269,7 +13269,7 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>294.11</v>
+        <v>295.55</v>
       </c>
     </row>
     <row r="211">
@@ -13330,7 +13330,7 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>36987.08</v>
+        <v>37168.77</v>
       </c>
     </row>
     <row r="212">
@@ -13391,7 +13391,7 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>77693.41</v>
+        <v>78075.06</v>
       </c>
     </row>
     <row r="213">
@@ -13452,7 +13452,7 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>133.68</v>
+        <v>134.34</v>
       </c>
     </row>
     <row r="214">
@@ -13513,7 +13513,7 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>2222.5</v>
+        <v>2229.87</v>
       </c>
     </row>
     <row r="215">
@@ -13574,7 +13574,7 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>13758.33</v>
+        <v>13803.97</v>
       </c>
     </row>
     <row r="216">
@@ -13635,7 +13635,7 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>382.65</v>
+        <v>383.92</v>
       </c>
     </row>
     <row r="217">
@@ -13696,7 +13696,7 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>13095.1</v>
+        <v>13138.54</v>
       </c>
     </row>
     <row r="218">
@@ -13757,7 +13757,7 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>31836.78</v>
+        <v>31942.39</v>
       </c>
     </row>
     <row r="219">
@@ -13818,7 +13818,7 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>68960.99000000001</v>
+        <v>69189.75999999999</v>
       </c>
     </row>
     <row r="220">
@@ -13879,7 +13879,7 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>70011.92</v>
+        <v>70244.17</v>
       </c>
     </row>
     <row r="221">
@@ -13940,7 +13940,7 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>71164.44</v>
+        <v>71400.52</v>
       </c>
     </row>
     <row r="222">
@@ -14001,7 +14001,7 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>45352.75</v>
+        <v>45503.2</v>
       </c>
     </row>
     <row r="223">
@@ -14062,7 +14062,7 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>50434.36</v>
+        <v>50601.66</v>
       </c>
     </row>
     <row r="224">
@@ -14123,7 +14123,7 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>2222.5</v>
+        <v>2229.87</v>
       </c>
     </row>
     <row r="225">
@@ -14184,7 +14184,7 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>7241.23</v>
+        <v>7265.25</v>
       </c>
     </row>
     <row r="226">
@@ -14245,7 +14245,7 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>30783.01</v>
+        <v>30885.13</v>
       </c>
     </row>
     <row r="227">
@@ -14306,7 +14306,7 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>12153.9</v>
+        <v>12194.22</v>
       </c>
     </row>
     <row r="228">
@@ -14367,7 +14367,7 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>37945.16</v>
+        <v>38071.04</v>
       </c>
     </row>
     <row r="229">
@@ -14428,7 +14428,7 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>294.11</v>
+        <v>295.08</v>
       </c>
     </row>
     <row r="230">
@@ -14489,7 +14489,7 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>776.5700000000001</v>
+        <v>779.15</v>
       </c>
     </row>
     <row r="231">
@@ -14550,7 +14550,7 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>32224.13</v>
+        <v>32331.03</v>
       </c>
     </row>
     <row r="232">
@@ -14611,7 +14611,7 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>23394.92</v>
+        <v>23472.53</v>
       </c>
     </row>
     <row r="233">
@@ -14672,7 +14672,7 @@
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>31750</v>
+        <v>31855.32</v>
       </c>
     </row>
     <row r="234">
@@ -14733,7 +14733,7 @@
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>29025.85</v>
+        <v>29122.13</v>
       </c>
     </row>
     <row r="235">
@@ -14794,7 +14794,7 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>37895.84</v>
+        <v>38021.56</v>
       </c>
     </row>
     <row r="236">
@@ -14855,7 +14855,7 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>49918.09</v>
+        <v>50076.96</v>
       </c>
     </row>
     <row r="237">
@@ -14916,7 +14916,7 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>36534.09</v>
+        <v>36650.37</v>
       </c>
     </row>
     <row r="238">
@@ -14977,7 +14977,7 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>57510.91</v>
+        <v>57693.96</v>
       </c>
     </row>
     <row r="239">
@@ -15038,7 +15038,7 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>17034.67</v>
+        <v>17088.88</v>
       </c>
     </row>
     <row r="240">
@@ -15099,7 +15099,7 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>9454.43</v>
+        <v>9484.52</v>
       </c>
     </row>
     <row r="241">
@@ -15160,7 +15160,7 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>46789.47</v>
+        <v>46938.39</v>
       </c>
     </row>
     <row r="242">
@@ -15221,7 +15221,7 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>1336.84</v>
+        <v>1341.1</v>
       </c>
     </row>
     <row r="243">
@@ -15282,7 +15282,7 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>10270.4</v>
+        <v>10303.09</v>
       </c>
     </row>
     <row r="244">
@@ -15343,7 +15343,7 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>23502.94</v>
+        <v>23577.74</v>
       </c>
     </row>
     <row r="245">
@@ -15404,7 +15404,7 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>10476.46</v>
+        <v>10509.8</v>
       </c>
     </row>
     <row r="246">
@@ -15465,7 +15465,7 @@
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>64156.02</v>
+        <v>64360.21</v>
       </c>
     </row>
     <row r="247">
@@ -15530,7 +15530,7 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>80282.56</v>
+        <v>80538.08</v>
       </c>
     </row>
     <row r="248">
@@ -15591,7 +15591,7 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>14482.45</v>
+        <v>14528.55</v>
       </c>
     </row>
     <row r="249">
@@ -15652,7 +15652,7 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>72651.41</v>
+        <v>72882.64</v>
       </c>
     </row>
     <row r="250">
@@ -15713,7 +15713,7 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>4533.9</v>
+        <v>4548.33</v>
       </c>
     </row>
     <row r="251">
@@ -15774,7 +15774,7 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>2116.67</v>
+        <v>2123.4</v>
       </c>
     </row>
     <row r="252">
@@ -15835,7 +15835,7 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>9486.110000000001</v>
+        <v>9516.299999999999</v>
       </c>
     </row>
     <row r="253">
@@ -15896,7 +15896,7 @@
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>1303.42</v>
+        <v>1310.35</v>
       </c>
     </row>
     <row r="254">
@@ -15961,7 +15961,7 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>82976.89</v>
+        <v>83418.11</v>
       </c>
     </row>
     <row r="255">
@@ -16022,7 +16022,7 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>36916.5</v>
+        <v>37112.8</v>
       </c>
     </row>
     <row r="256">
@@ -16083,7 +16083,7 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>13758.33</v>
+        <v>13831.49</v>
       </c>
     </row>
     <row r="257">
@@ -16144,7 +16144,7 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>209.55</v>
+        <v>210.66</v>
       </c>
     </row>
     <row r="258">
@@ -16205,7 +16205,7 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>22280.7</v>
+        <v>22399.18</v>
       </c>
     </row>
     <row r="259">
@@ -16266,7 +16266,7 @@
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>16048.46</v>
+        <v>16133.8</v>
       </c>
     </row>
     <row r="260">
@@ -16327,7 +16327,7 @@
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>628.85</v>
+        <v>632.1900000000001</v>
       </c>
     </row>
     <row r="261">
@@ -16388,7 +16388,7 @@
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>16712.46</v>
+        <v>16801.32</v>
       </c>
     </row>
     <row r="262">
@@ -16449,7 +16449,7 @@
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>1782.46</v>
+        <v>1791.93</v>
       </c>
     </row>
     <row r="263">
@@ -16510,7 +16510,7 @@
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>9004.83</v>
+        <v>9052.709999999999</v>
       </c>
     </row>
     <row r="264">
@@ -16571,7 +16571,7 @@
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>649.22</v>
+        <v>652.67</v>
       </c>
     </row>
     <row r="265">
@@ -16632,7 +16632,7 @@
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>61940.01</v>
+        <v>62269.37</v>
       </c>
     </row>
     <row r="266">
@@ -16693,7 +16693,7 @@
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>5344.67</v>
+        <v>5373.09</v>
       </c>
     </row>
     <row r="267">
@@ -16754,7 +16754,7 @@
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>2024.49</v>
+        <v>2035.25</v>
       </c>
     </row>
     <row r="268">
@@ -16815,7 +16815,7 @@
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>77982.45</v>
+        <v>78397.12</v>
       </c>
     </row>
     <row r="269">
@@ -16876,7 +16876,7 @@
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>31485.41</v>
+        <v>31652.84</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/administracion-y-entrega-de-beneficios/may-2026.xlsx
+++ b/docs/oc-mensuales/administracion-y-entrega-de-beneficios/may-2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC may-2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC may-2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -671,7 +671,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2261,7 +2261,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3542,7 +3542,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -4152,7 +4152,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4518,7 +4518,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4579,7 +4579,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -5067,7 +5067,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -6165,7 +6165,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -6287,7 +6287,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -7690,7 +7690,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -7812,7 +7812,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -8422,7 +8422,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -10557,7 +10557,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -10618,7 +10618,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -10740,7 +10740,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -10862,7 +10862,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -11228,7 +11228,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -11472,7 +11472,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -11792,7 +11792,7 @@
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
@@ -11857,7 +11857,7 @@
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
@@ -12029,7 +12029,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -13798,7 +13798,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -14042,7 +14042,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -15140,7 +15140,7 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
@@ -15445,7 +15445,7 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
@@ -15506,7 +15506,7 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
@@ -15521,7 +15521,7 @@
       </c>
       <c r="K247" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L247" t="inlineStr">
@@ -15571,7 +15571,7 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
@@ -15754,7 +15754,7 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
@@ -15952,7 +15952,7 @@
       </c>
       <c r="K254" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L254" t="inlineStr">
@@ -16368,7 +16368,7 @@
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
@@ -16429,7 +16429,7 @@
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
@@ -16490,7 +16490,7 @@
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">

--- a/docs/oc-mensuales/administracion-y-entrega-de-beneficios/may-2026.xlsx
+++ b/docs/oc-mensuales/administracion-y-entrega-de-beneficios/may-2026.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Comando de Personal</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección de Bienestar</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2008,7 +2008,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XI ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SEG PRIV CONTROL ARMAS Y EXPL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2622,7 +2622,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2683,7 +2683,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SEG PRIV CONTROL ARMAS Y EXPL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2927,7 +2927,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SEG PRIV CONTROL ARMAS Y EXPL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SEG PRIV CONTROL ARMAS Y EXPL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3232,7 +3232,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SEG PRIV CONTROL ARMAS Y EXPL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3720,7 +3720,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE</t>
+          <t>Hospital de Constitución</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3842,7 +3842,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE PUDAHUEL</t>
+          <t>MUNICIPALIDAD DE PUDAHUEL</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4025,7 +4025,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Dirección General de Carabineros de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4208,7 +4208,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Car</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4330,7 +4330,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4635,7 +4635,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dirección General de Carabineros de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Servicio Nacional de la Discapacidad</t>
+          <t>SERVICIO NACIONAL DE LA DISCAPACIDAD</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5128,7 +5128,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5189,7 +5189,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -5250,7 +5250,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -5367,7 +5367,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>HOSPITAL CLAUDIO VICUNA</t>
+          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5489,7 +5489,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5611,7 +5611,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5733,7 +5733,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5794,7 +5794,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SEG PRIV CONTROL ARMAS Y EXPL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5916,7 +5916,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SEG PRIV CONTROL ARMAS Y EXPL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -6038,7 +6038,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IX ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6221,7 +6221,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IX ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6343,7 +6343,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6709,7 +6709,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Dirección General de Carabineros de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -6770,7 +6770,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Zona Bienestar "Valparaíso" Bienestar Social</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -6953,7 +6953,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS X ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -7014,7 +7014,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS X ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7197,7 +7197,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7319,7 +7319,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS X ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7380,7 +7380,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hospital de Achao</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7563,7 +7563,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Dirección General de Carabineros de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -7807,7 +7807,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>VIII Zona de Carabineros Bio Bío</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -7868,7 +7868,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -7929,7 +7929,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -7990,7 +7990,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Dirección General de Carabineros de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -8051,7 +8051,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Carabineros de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -8112,7 +8112,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Hospital de Peñaflor</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE P</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -8163,7 +8163,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -8173,7 +8173,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Carabineros de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -8234,7 +8234,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Bienestar SSFFAA</t>
+          <t>SUBSECRETARIA PARA LAS FUERZAS ARMADAS</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -8417,7 +8417,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>HOSPITAL DE LITUECHE</t>
+          <t>Hospital de Litueche</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -8478,7 +8478,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XVI ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -8661,7 +8661,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>REGIMIENTO 12 "SANGRA"</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -8783,7 +8783,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>JEFATURA ADMINISTRATIVA Y LOGISTICA DE LA GUARNICION COYHAIQUE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -8905,7 +8905,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IX ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -9088,7 +9088,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Dirección Regional de Ñuble</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -9271,7 +9271,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -9454,7 +9454,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IX ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -9759,7 +9759,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -9881,7 +9881,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Dirección General de Carabineros de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -9942,7 +9942,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -10125,7 +10125,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Dirección General de Carabineros de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -10247,7 +10247,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Dirección General de Carabineros de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -10491,7 +10491,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Jefatura Adm y log Campo Militar Valdivia</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -10674,7 +10674,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -11223,7 +11223,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -11284,7 +11284,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -11650,7 +11650,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Servicio de Salud Atacama</t>
+          <t>SERVICIO DE SALUD ATACAMA</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -11953,7 +11953,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -11963,7 +11963,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Comité de Seguro Agricola</t>
+          <t>Comité de Seguros del Agro</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -12024,7 +12024,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -12146,7 +12146,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA CARAB ARAUCANÍA CONT ORD PUBL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -12207,7 +12207,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Hospital de Queilen</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -12268,7 +12268,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>DIRECCION DE INFANCIA</t>
+          <t>CORP MUNICIPAL MELIPILLA PARA LA ED SALUD</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -12329,7 +12329,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -12634,7 +12634,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Dirección Regional de Ñuble</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -12695,7 +12695,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XIV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -12756,7 +12756,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS V ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -12817,7 +12817,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -13000,7 +13000,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA CARAB ARAUCANÍA CONT ORD PUBL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -13061,7 +13061,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DEL TERRITORIO MARIT Y MM (AB)</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -13183,7 +13183,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SANTIAGO OESTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -13244,7 +13244,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Regimiento Logístico N° 1 "Tocopilla"</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -13427,7 +13427,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Departamento Provincial de Educación Osorno</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -13854,7 +13854,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS V ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -13915,7 +13915,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS V ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -13976,7 +13976,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS V ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -14281,7 +14281,7 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Consultorio General Urbano Victor Domingo Silva</t>
+          <t>CONSULTORIO GENERAL URBANO VICTOR DOMINGO SILVA</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -14403,7 +14403,7 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IX ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -14464,7 +14464,7 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>SII Oficina de Bienestar</t>
+          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -14525,7 +14525,7 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Carabineros de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -14708,7 +14708,7 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -14769,7 +14769,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Consultorio General Urbano San Felipe</t>
+          <t>CONSULTORIO GENERAL URBANO SAN FELIPE</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -15440,7 +15440,7 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>COMANDANCIA EN JEFE DE LA IIIa ZONA NAVAL</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -15688,7 +15688,7 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO DE BIENESTAR SOCIAL 1° Z.N.</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -16607,7 +16607,7 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS II ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -16790,7 +16790,7 @@
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Bienes y Servicios</t>
+          <t>Hospital de Melipilla</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">

--- a/docs/oc-mensuales/administracion-y-entrega-de-beneficios/may-2026.xlsx
+++ b/docs/oc-mensuales/administracion-y-entrega-de-beneficios/may-2026.xlsx
@@ -562,7 +562,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +822,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +887,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +952,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1017,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1082,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1147,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1212,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1277,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1342,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1407,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1472,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1537,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1602,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1667,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1732,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1797,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1862,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1927,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1992,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2057,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2122,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2187,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2252,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2274,7 +2382,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2335,7 +2447,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2396,7 +2512,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2457,7 +2577,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2518,7 +2642,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2579,7 +2707,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2640,7 +2772,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2701,7 +2837,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2762,7 +2902,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2823,7 +2967,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2884,7 +3032,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2945,7 +3097,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3006,7 +3162,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3067,7 +3227,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3128,7 +3292,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3189,7 +3357,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3250,7 +3422,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3311,7 +3487,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3372,7 +3552,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3433,7 +3617,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3494,7 +3682,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3555,7 +3747,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3616,7 +3812,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3677,7 +3877,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3738,7 +3942,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3799,7 +4007,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3860,7 +4072,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3921,7 +4137,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3982,7 +4202,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4043,7 +4267,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4104,7 +4332,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4165,7 +4397,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4226,7 +4462,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4287,7 +4527,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4348,7 +4592,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4409,7 +4657,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4470,7 +4722,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4531,7 +4787,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4592,7 +4852,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4653,7 +4917,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4714,7 +4982,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4775,7 +5047,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4836,7 +5112,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4897,7 +5177,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4958,7 +5242,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5019,7 +5307,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5080,7 +5372,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5141,7 +5437,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5202,7 +5502,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5263,7 +5567,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5324,7 +5632,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5385,7 +5697,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5446,7 +5762,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5507,7 +5827,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5568,7 +5892,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5629,7 +5957,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5690,7 +6022,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5751,7 +6087,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5812,7 +6152,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5873,7 +6217,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5934,7 +6282,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5995,7 +6347,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6056,7 +6412,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6117,7 +6477,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6178,7 +6542,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6239,7 +6607,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6300,7 +6672,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6361,7 +6737,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6422,7 +6802,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6483,7 +6867,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6544,7 +6932,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6605,7 +6997,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6666,7 +7062,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6727,7 +7127,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6788,7 +7192,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6849,7 +7257,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6910,7 +7322,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6971,7 +7387,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7032,7 +7452,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7093,7 +7517,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7154,7 +7582,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7215,7 +7647,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7276,7 +7712,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7337,7 +7777,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7398,7 +7842,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7459,7 +7907,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7520,7 +7972,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7581,7 +8037,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7642,7 +8102,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7703,7 +8167,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7764,7 +8232,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7825,7 +8297,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7886,7 +8362,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7947,7 +8427,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8008,7 +8492,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8069,7 +8557,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8130,7 +8622,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8191,7 +8687,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8252,7 +8752,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8313,7 +8817,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8374,7 +8882,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8435,7 +8947,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8496,7 +9012,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8557,7 +9077,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8618,7 +9142,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8679,7 +9207,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8740,7 +9272,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8801,7 +9337,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8862,7 +9402,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8923,7 +9467,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8984,7 +9532,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9045,7 +9597,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9106,7 +9662,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9167,7 +9727,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9228,7 +9792,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9289,7 +9857,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9350,7 +9922,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9411,7 +9987,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L147" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9472,7 +10052,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9533,7 +10117,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L149" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9594,7 +10182,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9655,7 +10247,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9716,7 +10312,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9777,7 +10377,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9838,7 +10442,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9899,7 +10507,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9960,7 +10572,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10021,7 +10637,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L157" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10082,7 +10702,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10143,7 +10767,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L159" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10204,7 +10832,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L160" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10265,7 +10897,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L161" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10326,7 +10962,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10387,7 +11027,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L163" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10448,7 +11092,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10509,7 +11157,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L165" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10570,7 +11222,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L166" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10631,7 +11287,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10692,7 +11352,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L168" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10753,7 +11417,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10814,7 +11482,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L170" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10875,7 +11547,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L171" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10936,7 +11612,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10997,7 +11677,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L173" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11058,7 +11742,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11119,7 +11807,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L175" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11180,7 +11872,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L176" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11241,7 +11937,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L177" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11302,7 +12002,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L178" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11363,7 +12067,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L179" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11424,7 +12132,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11485,7 +12197,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L181" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11546,7 +12262,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L182" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11607,7 +12327,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L183" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11668,7 +12392,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L184" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11729,7 +12457,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L185" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11920,7 +12652,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L188" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11981,7 +12717,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L189" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12042,7 +12782,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L190" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12103,7 +12847,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L191" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12164,7 +12912,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L192" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12225,7 +12977,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr"/>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L193" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12286,7 +13042,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr"/>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L194" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12347,7 +13107,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L195" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12408,7 +13172,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L196" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12469,7 +13237,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L197" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12530,7 +13302,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12591,7 +13367,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L199" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12652,7 +13432,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L200" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12713,7 +13497,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L201" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12774,7 +13562,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr"/>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L202" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12835,7 +13627,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr"/>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L203" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12896,7 +13692,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L204" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12957,7 +13757,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr"/>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L205" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13018,7 +13822,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr"/>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L206" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13079,7 +13887,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr"/>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L207" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13140,7 +13952,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr"/>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L208" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13201,7 +14017,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr"/>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L209" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13262,7 +14082,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr"/>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L210" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13323,7 +14147,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L211" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13384,7 +14212,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr"/>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L212" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13445,7 +14277,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L213" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13506,7 +14342,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr"/>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L214" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13567,7 +14407,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L215" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13628,7 +14472,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr"/>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L216" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13689,7 +14537,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr"/>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L217" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13750,7 +14602,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr"/>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L218" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13811,7 +14667,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr"/>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L219" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13872,7 +14732,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr"/>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L220" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13933,7 +14797,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr"/>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L221" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13994,7 +14862,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr"/>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L222" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14055,7 +14927,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr"/>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L223" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14116,7 +14992,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr"/>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L224" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14177,7 +15057,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr"/>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L225" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14238,7 +15122,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr"/>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L226" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14299,7 +15187,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr"/>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L227" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14360,7 +15252,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr"/>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L228" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14421,7 +15317,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr"/>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L229" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14482,7 +15382,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr"/>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L230" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14543,7 +15447,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr"/>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L231" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14604,7 +15512,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr"/>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L232" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14665,7 +15577,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr"/>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L233" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14726,7 +15642,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K234" t="inlineStr"/>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L234" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14787,7 +15707,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr"/>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L235" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14848,7 +15772,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr"/>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L236" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14909,7 +15837,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K237" t="inlineStr"/>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L237" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14970,7 +15902,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr"/>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L238" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15031,7 +15967,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr"/>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L239" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15092,7 +16032,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K240" t="inlineStr"/>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L240" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15153,7 +16097,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K241" t="inlineStr"/>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L241" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15214,7 +16162,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K242" t="inlineStr"/>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L242" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15275,7 +16227,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K243" t="inlineStr"/>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L243" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15336,7 +16292,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K244" t="inlineStr"/>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L244" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15397,7 +16357,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K245" t="inlineStr"/>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L245" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15458,7 +16422,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K246" t="inlineStr"/>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L246" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15584,7 +16552,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr"/>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L248" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15645,7 +16617,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr"/>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L249" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15706,7 +16682,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K250" t="inlineStr"/>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L250" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15767,7 +16747,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr"/>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L251" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15828,7 +16812,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K252" t="inlineStr"/>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L252" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15889,7 +16877,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K253" t="inlineStr"/>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L253" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16015,7 +17007,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K255" t="inlineStr"/>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L255" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16076,7 +17072,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K256" t="inlineStr"/>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L256" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16137,7 +17137,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K257" t="inlineStr"/>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L257" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16198,7 +17202,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K258" t="inlineStr"/>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L258" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16259,7 +17267,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K259" t="inlineStr"/>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L259" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16320,7 +17332,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr"/>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L260" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16381,7 +17397,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K261" t="inlineStr"/>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L261" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16442,7 +17462,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K262" t="inlineStr"/>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L262" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16503,7 +17527,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K263" t="inlineStr"/>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L263" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16564,7 +17592,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr"/>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L264" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16625,7 +17657,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K265" t="inlineStr"/>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L265" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16686,7 +17722,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K266" t="inlineStr"/>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L266" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16747,7 +17787,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K267" t="inlineStr"/>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L267" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16808,7 +17852,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K268" t="inlineStr"/>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L268" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16869,7 +17917,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K269" t="inlineStr"/>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L269" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/administracion-y-entrega-de-beneficios/may-2026.xlsx
+++ b/docs/oc-mensuales/administracion-y-entrega-de-beneficios/may-2026.xlsx
@@ -2939,7 +2939,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -10869,7 +10869,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
